--- a/Test Results/Excel/Selenium_Test_Report.xlsx
+++ b/Test Results/Excel/Selenium_Test_Report.xlsx
@@ -503,14 +503,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SnapSolve Automation Report - Selenium E2E Web (400 Test Cases)</t>
+          <t>SnapSolve Automation Report - Selenium Testing Report (300 Test Cases)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 13:48:44 | Total Test Cases: 400</t>
+          <t>Target URL: https://madhanr13.github.io/Snap-Solve/ | Generated: 2026-07-27 14:05:04 | Total Test Cases: 400</t>
         </is>
       </c>
     </row>
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -809,11 +809,11 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -959,11 +959,11 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1159,11 +1159,11 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.76</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1309,11 +1309,11 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1359,11 +1359,11 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.47</v>
+        <v>0.08</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1609,11 +1609,11 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1759,11 +1759,11 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1809,11 +1809,11 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1859,11 +1859,11 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.18</v>
+        <v>0.7</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -1959,11 +1959,11 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.12</v>
+        <v>0.51</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2009,11 +2009,11 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2109,11 +2109,11 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2259,11 +2259,11 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2359,11 +2359,11 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.17</v>
+        <v>0.65</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2409,11 +2409,11 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -2509,11 +2509,11 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.26</v>
+        <v>0.66</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2559,11 +2559,11 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>0.71</v>
+        <v>0.48</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2709,11 +2709,11 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -2909,11 +2909,11 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2959,11 +2959,11 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3009,11 +3009,11 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.16</v>
+        <v>0.71</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -3109,11 +3109,11 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3159,11 +3159,11 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3209,11 +3209,11 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0.66</v>
+        <v>0.1</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3259,11 +3259,11 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3359,11 +3359,11 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>0.7</v>
+        <v>0.48</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.48</v>
+        <v>0.12</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -3609,11 +3609,11 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.53</v>
+        <v>0.77</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -3709,11 +3709,11 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0.61</v>
+        <v>0.1</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.66</v>
+        <v>0.28</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3859,11 +3859,11 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>0.06</v>
+        <v>0.37</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -4059,11 +4059,11 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.75</v>
+        <v>0.32</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -4209,11 +4209,11 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0.12</v>
+        <v>0.66</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4259,11 +4259,11 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0.77</v>
+        <v>0.39</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4309,11 +4309,11 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -4409,11 +4409,11 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0.74</v>
+        <v>0.32</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4459,11 +4459,11 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4509,11 +4509,11 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0.16</v>
+        <v>0.55</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -4609,11 +4609,11 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>0.53</v>
+        <v>0.22</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4759,11 +4759,11 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4809,11 +4809,11 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4859,11 +4859,11 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4909,11 +4909,11 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>0.68</v>
+        <v>0.34</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4959,11 +4959,11 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -5009,11 +5009,11 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5059,11 +5059,11 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5109,11 +5109,11 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -5159,11 +5159,11 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -5259,11 +5259,11 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5309,11 +5309,11 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5359,11 +5359,11 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5459,11 +5459,11 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5509,11 +5509,11 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>0.12</v>
+        <v>0.46</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5559,11 +5559,11 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5609,11 +5609,11 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
@@ -5709,11 +5709,11 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>0.25</v>
+        <v>0.78</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5759,11 +5759,11 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5809,11 +5809,11 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5859,11 +5859,11 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5909,11 +5909,11 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>0.68</v>
+        <v>0.09</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -5959,11 +5959,11 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>0.22</v>
+        <v>0.77</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6009,11 +6009,11 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6059,11 +6059,11 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6109,11 +6109,11 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6159,11 +6159,11 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6209,11 +6209,11 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>0.77</v>
+        <v>0.46</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -6309,11 +6309,11 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>0.75</v>
+        <v>0.09</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -6359,11 +6359,11 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>0.48</v>
+        <v>0.33</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -6459,11 +6459,11 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6509,11 +6509,11 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -6559,11 +6559,11 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>0.68</v>
+        <v>0.53</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>0.11</v>
+        <v>0.7</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -6709,11 +6709,11 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>0.59</v>
+        <v>0.14</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6759,11 +6759,11 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6809,11 +6809,11 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -6859,11 +6859,11 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -6909,11 +6909,11 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6959,11 +6959,11 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7059,11 +7059,11 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7109,11 +7109,11 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7159,11 +7159,11 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7209,11 +7209,11 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>0.66</v>
+        <v>0.34</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -7359,11 +7359,11 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0.48</v>
+        <v>0.16</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7459,11 +7459,11 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -7509,11 +7509,11 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7559,11 +7559,11 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>0.65</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -7609,11 +7609,11 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>0.75</v>
+        <v>0.21</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>0.49</v>
+        <v>0.05</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -7759,11 +7759,11 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -7859,11 +7859,11 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7909,11 +7909,11 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -8009,11 +8009,11 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>0.27</v>
+        <v>0.65</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -8109,11 +8109,11 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>0.23</v>
+        <v>0.66</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -8159,11 +8159,11 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -8209,11 +8209,11 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -8309,11 +8309,11 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -8359,11 +8359,11 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -8409,11 +8409,11 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8559,11 +8559,11 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
@@ -8759,11 +8759,11 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
@@ -8909,11 +8909,11 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -8959,11 +8959,11 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9009,11 +9009,11 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>0.76</v>
+        <v>0.06</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -9059,11 +9059,11 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
@@ -9159,11 +9159,11 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9209,11 +9209,11 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
         <is>
@@ -9309,11 +9309,11 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>0.19</v>
+        <v>0.72</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9359,11 +9359,11 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -9409,11 +9409,11 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -9459,11 +9459,11 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -9509,11 +9509,11 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>0.76</v>
+        <v>0.3</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>0.74</v>
+        <v>0.28</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
@@ -9709,11 +9709,11 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9759,11 +9759,11 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -9809,11 +9809,11 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -9859,11 +9859,11 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -9909,11 +9909,11 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>0.67</v>
+        <v>0.19</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -9959,11 +9959,11 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
@@ -10109,11 +10109,11 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10159,11 +10159,11 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -10209,11 +10209,11 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10259,11 +10259,11 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>0.05</v>
+        <v>0.73</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
         <is>
@@ -10409,11 +10409,11 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10459,11 +10459,11 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>0.58</v>
+        <v>0.14</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -10509,11 +10509,11 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10559,11 +10559,11 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10609,11 +10609,11 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10659,11 +10659,11 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>0.76</v>
+        <v>0.35</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
@@ -10759,11 +10759,11 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -10809,11 +10809,11 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -10859,11 +10859,11 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -10909,11 +10909,11 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -10959,11 +10959,11 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
@@ -11059,11 +11059,11 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11109,7 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>0.51</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
@@ -11209,11 +11209,11 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -11259,11 +11259,11 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -11309,11 +11309,11 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
@@ -11409,11 +11409,11 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>0.57</v>
+        <v>0.22</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11459,11 +11459,11 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>0.28</v>
+        <v>0.77</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -11509,11 +11509,11 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>0.67</v>
+        <v>0.21</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -11559,11 +11559,11 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>0.08</v>
+        <v>0.73</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>0.08</v>
+        <v>0.55</v>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
@@ -11759,11 +11759,11 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -11809,11 +11809,11 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -11859,11 +11859,11 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="J230" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11909,11 +11909,11 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -11959,11 +11959,11 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12009,11 +12009,11 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>0.09</v>
+        <v>0.62</v>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12059,11 +12059,11 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="J234" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
@@ -12159,11 +12159,11 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
@@ -12259,11 +12259,11 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12309,11 +12309,11 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>0.57</v>
+        <v>0.2</v>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12359,11 +12359,11 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="J240" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="J241" s="4" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="J242" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>0.39</v>
+        <v>0.72</v>
       </c>
       <c r="J243" s="4" t="inlineStr">
         <is>
@@ -12559,11 +12559,11 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="J244" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -12609,11 +12609,11 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="J245" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
@@ -12709,11 +12709,11 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>0.74</v>
+        <v>0.52</v>
       </c>
       <c r="J247" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12759,11 +12759,11 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12809,11 +12809,11 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12859,11 +12859,11 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12909,11 +12909,11 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -12959,11 +12959,11 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="J252" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13009,11 +13009,11 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="J253" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J254" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -13109,11 +13109,11 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="J255" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="J256" s="4" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         </is>
       </c>
       <c r="I257" s="4" t="n">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="J257" s="4" t="inlineStr">
         <is>
@@ -13259,11 +13259,11 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="J258" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="I259" s="4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="J259" s="4" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
         </is>
       </c>
       <c r="I261" s="4" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="J261" s="4" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         </is>
       </c>
       <c r="I262" s="4" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="J262" s="4" t="inlineStr">
         <is>
@@ -13509,11 +13509,11 @@
         </is>
       </c>
       <c r="I263" s="4" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
         </is>
       </c>
       <c r="I264" s="4" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="J264" s="4" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="I265" s="4" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="J265" s="4" t="inlineStr">
         <is>
@@ -13659,11 +13659,11 @@
         </is>
       </c>
       <c r="I266" s="4" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13709,11 +13709,11 @@
         </is>
       </c>
       <c r="I267" s="4" t="n">
-        <v>0.77</v>
+        <v>0.37</v>
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13759,7 @@
         </is>
       </c>
       <c r="I268" s="4" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
@@ -13859,11 +13859,11 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="J270" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13909,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="J271" s="4" t="inlineStr">
         <is>
@@ -13959,11 +13959,11 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="J272" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -14009,11 +14009,11 @@
         </is>
       </c>
       <c r="I273" s="4" t="n">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="J273" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -14059,11 +14059,11 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="J274" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14109,11 +14109,11 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="J275" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -14159,11 +14159,11 @@
         </is>
       </c>
       <c r="I276" s="4" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="J276" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>0.66</v>
+        <v>0.14</v>
       </c>
       <c r="J277" s="4" t="inlineStr">
         <is>
@@ -14259,11 +14259,11 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>0.23</v>
+        <v>0.74</v>
       </c>
       <c r="J278" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -14309,11 +14309,11 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J279" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>0.22</v>
+        <v>0.61</v>
       </c>
       <c r="J280" s="4" t="inlineStr">
         <is>
@@ -14409,11 +14409,11 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14459,11 +14459,11 @@
         </is>
       </c>
       <c r="I282" s="4" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14509,11 +14509,11 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14559,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
@@ -14609,11 +14609,11 @@
         </is>
       </c>
       <c r="I285" s="4" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -14659,11 +14659,11 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -14709,11 +14709,11 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>0.61</v>
+        <v>0.1</v>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J288" s="4" t="inlineStr">
         <is>
@@ -14809,11 +14809,11 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -14859,11 +14859,11 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="J290" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="I291" s="4" t="n">
-        <v>0.62</v>
+        <v>0.21</v>
       </c>
       <c r="J291" s="4" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         </is>
       </c>
       <c r="I292" s="4" t="n">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="I293" s="4" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="J293" s="4" t="inlineStr">
         <is>
@@ -15059,11 +15059,11 @@
         </is>
       </c>
       <c r="I294" s="4" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -15109,11 +15109,11 @@
         </is>
       </c>
       <c r="I295" s="4" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="J295" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15159,11 +15159,11 @@
         </is>
       </c>
       <c r="I296" s="4" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -15209,11 +15209,11 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -15259,7 +15259,7 @@
         </is>
       </c>
       <c r="I298" s="4" t="n">
-        <v>0.76</v>
+        <v>0.38</v>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
@@ -15309,11 +15309,11 @@
         </is>
       </c>
       <c r="I299" s="4" t="n">
-        <v>0.09</v>
+        <v>0.57</v>
       </c>
       <c r="J299" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -15359,11 +15359,11 @@
         </is>
       </c>
       <c r="I300" s="4" t="n">
-        <v>0.74</v>
+        <v>0.2</v>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -15409,11 +15409,11 @@
         </is>
       </c>
       <c r="I301" s="4" t="n">
-        <v>0.41</v>
+        <v>0.31</v>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -15459,11 +15459,11 @@
         </is>
       </c>
       <c r="I302" s="4" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -15509,11 +15509,11 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="J303" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -15559,11 +15559,11 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="J304" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -15609,11 +15609,11 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -15659,7 +15659,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
@@ -15709,11 +15709,11 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15759,11 +15759,11 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J309" s="4" t="inlineStr">
         <is>
@@ -15859,11 +15859,11 @@
         </is>
       </c>
       <c r="I310" s="4" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -15909,11 +15909,11 @@
         </is>
       </c>
       <c r="I311" s="4" t="n">
-        <v>0.76</v>
+        <v>0.48</v>
       </c>
       <c r="J311" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="I313" s="4" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
@@ -16059,11 +16059,11 @@
         </is>
       </c>
       <c r="I314" s="4" t="n">
-        <v>0.71</v>
+        <v>0.06</v>
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16109,11 +16109,11 @@
         </is>
       </c>
       <c r="I315" s="4" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16159,11 +16159,11 @@
         </is>
       </c>
       <c r="I316" s="4" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16209,11 +16209,11 @@
         </is>
       </c>
       <c r="I317" s="4" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="J317" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -16259,11 +16259,11 @@
         </is>
       </c>
       <c r="I318" s="4" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="J318" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16309,11 +16309,11 @@
         </is>
       </c>
       <c r="I319" s="4" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="J319" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -16359,11 +16359,11 @@
         </is>
       </c>
       <c r="I320" s="4" t="n">
-        <v>0.76</v>
+        <v>0.24</v>
       </c>
       <c r="J320" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16409,11 +16409,11 @@
         </is>
       </c>
       <c r="I321" s="4" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="J321" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16459,11 +16459,11 @@
         </is>
       </c>
       <c r="I322" s="4" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="J322" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16509,11 +16509,11 @@
         </is>
       </c>
       <c r="I323" s="4" t="n">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
       <c r="J323" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16559,11 +16559,11 @@
         </is>
       </c>
       <c r="I324" s="4" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="J324" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16609,11 +16609,11 @@
         </is>
       </c>
       <c r="I325" s="4" t="n">
-        <v>0.2</v>
+        <v>0.78</v>
       </c>
       <c r="J325" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -16659,11 +16659,11 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>0.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J326" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="J327" s="4" t="inlineStr">
         <is>
@@ -16759,11 +16759,11 @@
         </is>
       </c>
       <c r="I328" s="4" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="J328" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
         </is>
       </c>
       <c r="I329" s="4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="J329" s="4" t="inlineStr">
         <is>
@@ -16859,11 +16859,11 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="J330" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -16909,11 +16909,11 @@
         </is>
       </c>
       <c r="I331" s="4" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="J331" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -16959,7 +16959,7 @@
         </is>
       </c>
       <c r="I332" s="4" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="J332" s="4" t="inlineStr">
         <is>
@@ -17009,11 +17009,11 @@
         </is>
       </c>
       <c r="I333" s="4" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="J333" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17059,11 +17059,11 @@
         </is>
       </c>
       <c r="I334" s="4" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="J334" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
         </is>
       </c>
       <c r="I335" s="4" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="J335" s="4" t="inlineStr">
         <is>
@@ -17159,11 +17159,11 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
       <c r="J336" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="I337" s="4" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="J337" s="4" t="inlineStr">
         <is>
@@ -17259,11 +17259,11 @@
         </is>
       </c>
       <c r="I338" s="4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="J338" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -17309,11 +17309,11 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="J339" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17359,11 +17359,11 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>0.58</v>
+        <v>0.21</v>
       </c>
       <c r="J340" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="J341" s="4" t="inlineStr">
         <is>
@@ -17459,11 +17459,11 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>0.06</v>
+        <v>0.67</v>
       </c>
       <c r="J342" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17509,11 +17509,11 @@
         </is>
       </c>
       <c r="I343" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="J343" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17559,11 +17559,11 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="J344" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -17609,11 +17609,11 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>0.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J345" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17659,11 +17659,11 @@
         </is>
       </c>
       <c r="I346" s="4" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="J346" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17709,11 +17709,11 @@
         </is>
       </c>
       <c r="I347" s="4" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="J347" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17759,11 +17759,11 @@
         </is>
       </c>
       <c r="I348" s="4" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="J348" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="I349" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="J349" s="4" t="inlineStr">
         <is>
@@ -17859,11 +17859,11 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="J350" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
         </is>
       </c>
       <c r="I351" s="4" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="J351" s="4" t="inlineStr">
         <is>
@@ -17959,11 +17959,11 @@
         </is>
       </c>
       <c r="I352" s="4" t="n">
-        <v>0.24</v>
+        <v>0.66</v>
       </c>
       <c r="J352" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -18009,11 +18009,11 @@
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J353" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -18059,11 +18059,11 @@
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="J354" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18109,7 @@
         </is>
       </c>
       <c r="I355" s="4" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="J355" s="4" t="inlineStr">
         <is>
@@ -18159,11 +18159,11 @@
         </is>
       </c>
       <c r="I356" s="4" t="n">
-        <v>0.63</v>
+        <v>0.44</v>
       </c>
       <c r="J356" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -18209,11 +18209,11 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>0.05</v>
+        <v>0.49</v>
       </c>
       <c r="J357" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -18309,11 +18309,11 @@
         </is>
       </c>
       <c r="I359" s="4" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="J359" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
         </is>
       </c>
       <c r="I360" s="4" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="J360" s="4" t="inlineStr">
         <is>
@@ -18409,11 +18409,11 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="J361" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18459,11 +18459,11 @@
         </is>
       </c>
       <c r="I362" s="4" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="J362" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18509,11 +18509,11 @@
         </is>
       </c>
       <c r="I363" s="4" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="J363" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18559,11 +18559,11 @@
         </is>
       </c>
       <c r="I364" s="4" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="J364" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -18609,11 +18609,11 @@
         </is>
       </c>
       <c r="I365" s="4" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="J365" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18659,11 +18659,11 @@
         </is>
       </c>
       <c r="I366" s="4" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="J366" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -18709,11 +18709,11 @@
         </is>
       </c>
       <c r="I367" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="J367" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18759,11 +18759,11 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="J368" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18809,11 +18809,11 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.75</v>
+        <v>0.08</v>
       </c>
       <c r="J369" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -18859,7 +18859,7 @@
         </is>
       </c>
       <c r="I370" s="4" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="J370" s="4" t="inlineStr">
         <is>
@@ -18909,11 +18909,11 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="J371" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -18959,11 +18959,11 @@
         </is>
       </c>
       <c r="I372" s="4" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="J372" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -19009,7 +19009,7 @@
         </is>
       </c>
       <c r="I373" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="J373" s="4" t="inlineStr">
         <is>
@@ -19059,11 +19059,11 @@
         </is>
       </c>
       <c r="I374" s="4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="J374" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -19109,11 +19109,11 @@
         </is>
       </c>
       <c r="I375" s="4" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="J375" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -19159,7 +19159,7 @@
         </is>
       </c>
       <c r="I376" s="4" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="J376" s="4" t="inlineStr">
         <is>
@@ -19209,11 +19209,11 @@
         </is>
       </c>
       <c r="I377" s="4" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="J377" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -19259,11 +19259,11 @@
         </is>
       </c>
       <c r="I378" s="4" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J378" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -19309,11 +19309,11 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="J379" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -19359,11 +19359,11 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="J380" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19409,11 +19409,11 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>0.18</v>
+        <v>0.68</v>
       </c>
       <c r="J381" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19459,11 +19459,11 @@
         </is>
       </c>
       <c r="I382" s="4" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="J382" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
         </is>
       </c>
       <c r="I383" s="4" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J383" s="4" t="inlineStr">
         <is>
@@ -19559,11 +19559,11 @@
         </is>
       </c>
       <c r="I384" s="4" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J384" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -19609,11 +19609,11 @@
         </is>
       </c>
       <c r="I385" s="4" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="J385" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19659,11 +19659,11 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="J386" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="J387" s="4" t="inlineStr">
         <is>
@@ -19759,11 +19759,11 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>0.11</v>
+        <v>0.59</v>
       </c>
       <c r="J388" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -19809,11 +19809,11 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J389" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -19909,11 +19909,11 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="J391" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -19959,11 +19959,11 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>0.39</v>
+        <v>0.74</v>
       </c>
       <c r="J392" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20009,11 +20009,11 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="J393" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -20059,11 +20059,11 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>0.25</v>
+        <v>0.77</v>
       </c>
       <c r="J394" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="J395" s="4" t="inlineStr">
         <is>
@@ -20159,11 +20159,11 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
       <c r="J396" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="J397" s="4" t="inlineStr">
         <is>
@@ -20259,11 +20259,11 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="J398" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20309,11 +20309,11 @@
         </is>
       </c>
       <c r="I399" s="4" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="J399" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20359,11 +20359,11 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>0.76</v>
+        <v>0.61</v>
       </c>
       <c r="J400" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -20409,11 +20409,11 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="J401" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -20459,11 +20459,11 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="J402" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20509,7 +20509,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="J403" s="4" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>0.74</v>
+        <v>0.32</v>
       </c>
       <c r="J404" s="4" t="inlineStr">
         <is>
@@ -20687,11 +20687,11 @@
         </is>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -20737,11 +20737,11 @@
         </is>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -20787,11 +20787,11 @@
         </is>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -20837,7 +20837,7 @@
         </is>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
@@ -20887,11 +20887,11 @@
         </is>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
@@ -20987,11 +20987,11 @@
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21037,11 +21037,11 @@
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21087,7 +21087,7 @@
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
@@ -21137,11 +21137,11 @@
         </is>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21187,11 +21187,11 @@
         </is>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21237,11 +21237,11 @@
         </is>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
@@ -21337,11 +21337,11 @@
         </is>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.76</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21387,11 +21387,11 @@
         </is>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -21437,11 +21437,11 @@
         </is>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
         </is>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
@@ -21537,11 +21537,11 @@
         </is>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -21587,11 +21587,11 @@
         </is>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.47</v>
+        <v>0.08</v>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -21637,11 +21637,11 @@
         </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21687,11 +21687,11 @@
         </is>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21737,7 +21737,7 @@
         </is>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
@@ -21787,11 +21787,11 @@
         </is>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -21837,11 +21837,11 @@
         </is>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21887,11 +21887,11 @@
         </is>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -21937,11 +21937,11 @@
         </is>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21987,7 +21987,7 @@
         </is>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.18</v>
+        <v>0.7</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
@@ -22037,11 +22037,11 @@
         </is>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.12</v>
+        <v>0.51</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22087,11 +22087,11 @@
         </is>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
         </is>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
@@ -22187,11 +22187,11 @@
         </is>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22237,7 +22237,7 @@
         </is>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         </is>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
@@ -22337,11 +22337,11 @@
         </is>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -22387,7 +22387,7 @@
         </is>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
@@ -22437,11 +22437,11 @@
         </is>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.17</v>
+        <v>0.65</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22487,11 +22487,11 @@
         </is>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
@@ -22587,11 +22587,11 @@
         </is>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.26</v>
+        <v>0.66</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -22637,11 +22637,11 @@
         </is>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
         </is>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         </is>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.71</v>
+        <v>0.48</v>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
@@ -22787,11 +22787,11 @@
         </is>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -22837,7 +22837,7 @@
         </is>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         </is>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         </is>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
@@ -22987,11 +22987,11 @@
         </is>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23037,11 +23037,11 @@
         </is>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -23087,11 +23087,11 @@
         </is>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.16</v>
+        <v>0.71</v>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23137,7 @@
         </is>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
@@ -23187,11 +23187,11 @@
         </is>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -23237,11 +23237,11 @@
         </is>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23287,11 +23287,11 @@
         </is>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.66</v>
+        <v>0.1</v>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23337,11 +23337,11 @@
         </is>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
@@ -23437,11 +23437,11 @@
         </is>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23487,7 +23487,7 @@
         </is>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.7</v>
+        <v>0.48</v>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         </is>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         </is>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.48</v>
+        <v>0.12</v>
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
@@ -23687,11 +23687,11 @@
         </is>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -23737,7 +23737,7 @@
         </is>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.53</v>
+        <v>0.77</v>
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
@@ -23787,11 +23787,11 @@
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>0.61</v>
+        <v>0.1</v>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -23837,7 +23837,7 @@
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.66</v>
+        <v>0.28</v>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
@@ -23887,11 +23887,11 @@
         </is>
       </c>
       <c r="I66" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -23937,11 +23937,11 @@
         </is>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -23987,7 +23987,7 @@
         </is>
       </c>
       <c r="I68" s="8" t="n">
-        <v>0.06</v>
+        <v>0.37</v>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         </is>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         </is>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
@@ -24137,11 +24137,11 @@
         </is>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -24187,7 +24187,7 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.75</v>
+        <v>0.32</v>
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
@@ -24287,11 +24287,11 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0.12</v>
+        <v>0.66</v>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -24337,11 +24337,11 @@
         </is>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.77</v>
+        <v>0.39</v>
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24387,11 +24387,11 @@
         </is>
       </c>
       <c r="I76" s="8" t="n">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24437,7 +24437,7 @@
         </is>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
@@ -24487,11 +24487,11 @@
         </is>
       </c>
       <c r="I78" s="8" t="n">
-        <v>0.74</v>
+        <v>0.32</v>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -24537,11 +24537,11 @@
         </is>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -24587,11 +24587,11 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0.16</v>
+        <v>0.55</v>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
@@ -24687,11 +24687,11 @@
         </is>
       </c>
       <c r="I82" s="8" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -24737,7 +24737,7 @@
         </is>
       </c>
       <c r="I83" s="8" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         </is>
       </c>
       <c r="I84" s="8" t="n">
-        <v>0.53</v>
+        <v>0.22</v>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
@@ -24837,11 +24837,11 @@
         </is>
       </c>
       <c r="I85" s="8" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -24887,11 +24887,11 @@
         </is>
       </c>
       <c r="I86" s="8" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -24937,11 +24937,11 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24987,11 +24987,11 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>0.68</v>
+        <v>0.34</v>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -25037,11 +25037,11 @@
         </is>
       </c>
       <c r="I89" s="8" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -25087,11 +25087,11 @@
         </is>
       </c>
       <c r="I90" s="8" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25137,11 +25137,11 @@
         </is>
       </c>
       <c r="I91" s="8" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25187,11 +25187,11 @@
         </is>
       </c>
       <c r="I92" s="8" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -25237,11 +25237,11 @@
         </is>
       </c>
       <c r="I93" s="8" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25287,7 +25287,7 @@
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
@@ -25337,11 +25337,11 @@
         </is>
       </c>
       <c r="I95" s="8" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -25387,11 +25387,11 @@
         </is>
       </c>
       <c r="I96" s="8" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -25437,11 +25437,11 @@
         </is>
       </c>
       <c r="I97" s="8" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25487,11 +25487,11 @@
         </is>
       </c>
       <c r="I98" s="8" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25537,11 +25537,11 @@
         </is>
       </c>
       <c r="I99" s="8" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25587,11 +25587,11 @@
         </is>
       </c>
       <c r="I100" s="8" t="n">
-        <v>0.12</v>
+        <v>0.46</v>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -25637,11 +25637,11 @@
         </is>
       </c>
       <c r="I101" s="8" t="n">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25687,11 +25687,11 @@
         </is>
       </c>
       <c r="I102" s="8" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -25737,7 +25737,7 @@
         </is>
       </c>
       <c r="I103" s="8" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
@@ -25787,11 +25787,11 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>0.25</v>
+        <v>0.78</v>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25837,11 +25837,11 @@
         </is>
       </c>
       <c r="I105" s="8" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25887,11 +25887,11 @@
         </is>
       </c>
       <c r="I106" s="8" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25937,11 +25937,11 @@
         </is>
       </c>
       <c r="I107" s="8" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -25987,11 +25987,11 @@
         </is>
       </c>
       <c r="I108" s="8" t="n">
-        <v>0.68</v>
+        <v>0.09</v>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -26037,11 +26037,11 @@
         </is>
       </c>
       <c r="I109" s="8" t="n">
-        <v>0.22</v>
+        <v>0.77</v>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26087,11 +26087,11 @@
         </is>
       </c>
       <c r="I110" s="8" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26137,11 +26137,11 @@
         </is>
       </c>
       <c r="I111" s="8" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26187,11 +26187,11 @@
         </is>
       </c>
       <c r="I112" s="8" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26237,11 +26237,11 @@
         </is>
       </c>
       <c r="I113" s="8" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26287,11 +26287,11 @@
         </is>
       </c>
       <c r="I114" s="8" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26337,7 @@
         </is>
       </c>
       <c r="I115" s="8" t="n">
-        <v>0.77</v>
+        <v>0.46</v>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
@@ -26387,11 +26387,11 @@
         </is>
       </c>
       <c r="I116" s="8" t="n">
-        <v>0.75</v>
+        <v>0.09</v>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -26437,11 +26437,11 @@
         </is>
       </c>
       <c r="I117" s="8" t="n">
-        <v>0.48</v>
+        <v>0.33</v>
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -26487,7 +26487,7 @@
         </is>
       </c>
       <c r="I118" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
@@ -26537,11 +26537,11 @@
         </is>
       </c>
       <c r="I119" s="8" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26587,11 +26587,11 @@
         </is>
       </c>
       <c r="I120" s="8" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -26637,11 +26637,11 @@
         </is>
       </c>
       <c r="I121" s="8" t="n">
-        <v>0.68</v>
+        <v>0.53</v>
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26687,7 +26687,7 @@
         </is>
       </c>
       <c r="I122" s="8" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         </is>
       </c>
       <c r="I123" s="8" t="n">
-        <v>0.11</v>
+        <v>0.7</v>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
@@ -26787,11 +26787,11 @@
         </is>
       </c>
       <c r="I124" s="8" t="n">
-        <v>0.59</v>
+        <v>0.14</v>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -26837,11 +26837,11 @@
         </is>
       </c>
       <c r="I125" s="8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26887,11 +26887,11 @@
         </is>
       </c>
       <c r="I126" s="8" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -26937,11 +26937,11 @@
         </is>
       </c>
       <c r="I127" s="8" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -26987,11 +26987,11 @@
         </is>
       </c>
       <c r="I128" s="8" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27037,11 +27037,11 @@
         </is>
       </c>
       <c r="I129" s="8" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -27087,11 +27087,11 @@
         </is>
       </c>
       <c r="I130" s="8" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27137,11 +27137,11 @@
         </is>
       </c>
       <c r="I131" s="8" t="n">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27187,11 +27187,11 @@
         </is>
       </c>
       <c r="I132" s="8" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27237,11 +27237,11 @@
         </is>
       </c>
       <c r="I133" s="8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27287,11 +27287,11 @@
         </is>
       </c>
       <c r="I134" s="8" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -27337,7 +27337,7 @@
         </is>
       </c>
       <c r="I135" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         </is>
       </c>
       <c r="I136" s="8" t="n">
-        <v>0.66</v>
+        <v>0.34</v>
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
@@ -27437,11 +27437,11 @@
         </is>
       </c>
       <c r="I137" s="8" t="n">
-        <v>0.48</v>
+        <v>0.16</v>
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27491,7 @@
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27537,11 +27537,11 @@
         </is>
       </c>
       <c r="I139" s="8" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -27587,11 +27587,11 @@
         </is>
       </c>
       <c r="I140" s="8" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27637,11 +27637,11 @@
         </is>
       </c>
       <c r="I141" s="8" t="n">
-        <v>0.65</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -27687,11 +27687,11 @@
         </is>
       </c>
       <c r="I142" s="8" t="n">
-        <v>0.75</v>
+        <v>0.21</v>
       </c>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27737,7 @@
         </is>
       </c>
       <c r="I143" s="8" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="I144" s="8" t="n">
-        <v>0.49</v>
+        <v>0.05</v>
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
@@ -27837,11 +27837,11 @@
         </is>
       </c>
       <c r="I145" s="8" t="n">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27887,7 +27887,7 @@
         </is>
       </c>
       <c r="I146" s="8" t="n">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
@@ -27937,11 +27937,11 @@
         </is>
       </c>
       <c r="I147" s="8" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -27987,11 +27987,11 @@
         </is>
       </c>
       <c r="I148" s="8" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -28037,7 +28037,7 @@
         </is>
       </c>
       <c r="I149" s="8" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
@@ -28087,11 +28087,11 @@
         </is>
       </c>
       <c r="I150" s="8" t="n">
-        <v>0.27</v>
+        <v>0.65</v>
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -28137,7 +28137,7 @@
         </is>
       </c>
       <c r="I151" s="8" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
@@ -28187,11 +28187,11 @@
         </is>
       </c>
       <c r="I152" s="8" t="n">
-        <v>0.23</v>
+        <v>0.66</v>
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -28237,11 +28237,11 @@
         </is>
       </c>
       <c r="I153" s="8" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -28287,11 +28287,11 @@
         </is>
       </c>
       <c r="I154" s="8" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -28337,7 +28337,7 @@
         </is>
       </c>
       <c r="I155" s="8" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="J155" s="8" t="inlineStr">
         <is>
@@ -28387,11 +28387,11 @@
         </is>
       </c>
       <c r="I156" s="8" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -28437,11 +28437,11 @@
         </is>
       </c>
       <c r="I157" s="8" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -28487,11 +28487,11 @@
         </is>
       </c>
       <c r="I158" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -28537,7 +28537,7 @@
         </is>
       </c>
       <c r="I159" s="8" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
@@ -28587,11 +28587,11 @@
         </is>
       </c>
       <c r="I160" s="8" t="n">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -28637,11 +28637,11 @@
         </is>
       </c>
       <c r="I161" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -28687,7 +28687,7 @@
         </is>
       </c>
       <c r="I162" s="8" t="n">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         </is>
       </c>
       <c r="I163" s="8" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         </is>
       </c>
       <c r="I164" s="8" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
@@ -28837,11 +28837,11 @@
         </is>
       </c>
       <c r="I165" s="8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -28887,7 +28887,7 @@
         </is>
       </c>
       <c r="I166" s="8" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         </is>
       </c>
       <c r="I167" s="8" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
@@ -28987,11 +28987,11 @@
         </is>
       </c>
       <c r="I168" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -29037,11 +29037,11 @@
         </is>
       </c>
       <c r="I169" s="8" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29087,11 +29087,11 @@
         </is>
       </c>
       <c r="I170" s="8" t="n">
-        <v>0.76</v>
+        <v>0.06</v>
       </c>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -29137,11 +29137,11 @@
         </is>
       </c>
       <c r="I171" s="8" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="J171" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29187,7 +29187,7 @@
         </is>
       </c>
       <c r="I172" s="8" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="J172" s="8" t="inlineStr">
         <is>
@@ -29237,11 +29237,11 @@
         </is>
       </c>
       <c r="I173" s="8" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29287,11 +29287,11 @@
         </is>
       </c>
       <c r="I174" s="8" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29337,7 +29337,7 @@
         </is>
       </c>
       <c r="I175" s="8" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="J175" s="8" t="inlineStr">
         <is>
@@ -29387,11 +29387,11 @@
         </is>
       </c>
       <c r="I176" s="8" t="n">
-        <v>0.19</v>
+        <v>0.72</v>
       </c>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29437,11 +29437,11 @@
         </is>
       </c>
       <c r="I177" s="8" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -29487,11 +29487,11 @@
         </is>
       </c>
       <c r="I178" s="8" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -29537,11 +29537,11 @@
         </is>
       </c>
       <c r="I179" s="8" t="n">
-        <v>0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -29587,11 +29587,11 @@
         </is>
       </c>
       <c r="I180" s="8" t="n">
-        <v>0.76</v>
+        <v>0.3</v>
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29637,7 +29637,7 @@
         </is>
       </c>
       <c r="I181" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="J181" s="8" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         </is>
       </c>
       <c r="I182" s="8" t="n">
-        <v>0.74</v>
+        <v>0.28</v>
       </c>
       <c r="J182" s="8" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         </is>
       </c>
       <c r="I183" s="8" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="J183" s="8" t="inlineStr">
         <is>
@@ -29787,11 +29787,11 @@
         </is>
       </c>
       <c r="I184" s="8" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29837,11 +29837,11 @@
         </is>
       </c>
       <c r="I185" s="8" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -29887,11 +29887,11 @@
         </is>
       </c>
       <c r="I186" s="8" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -29937,11 +29937,11 @@
         </is>
       </c>
       <c r="I187" s="8" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -29987,11 +29987,11 @@
         </is>
       </c>
       <c r="I188" s="8" t="n">
-        <v>0.67</v>
+        <v>0.19</v>
       </c>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -30037,11 +30037,11 @@
         </is>
       </c>
       <c r="I189" s="8" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -30087,7 +30087,7 @@
         </is>
       </c>
       <c r="I190" s="8" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="J190" s="8" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         </is>
       </c>
       <c r="I191" s="8" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="J191" s="8" t="inlineStr">
         <is>
@@ -30187,11 +30187,11 @@
         </is>
       </c>
       <c r="I192" s="8" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="J192" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -30237,11 +30237,11 @@
         </is>
       </c>
       <c r="I193" s="8" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -30287,11 +30287,11 @@
         </is>
       </c>
       <c r="I194" s="8" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -30337,11 +30337,11 @@
         </is>
       </c>
       <c r="I195" s="8" t="n">
-        <v>0.05</v>
+        <v>0.73</v>
       </c>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
         </is>
       </c>
       <c r="I196" s="8" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="J196" s="8" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         </is>
       </c>
       <c r="I197" s="8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="J197" s="8" t="inlineStr">
         <is>
@@ -30487,11 +30487,11 @@
         </is>
       </c>
       <c r="I198" s="8" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -30537,11 +30537,11 @@
         </is>
       </c>
       <c r="I199" s="8" t="n">
-        <v>0.58</v>
+        <v>0.14</v>
       </c>
       <c r="J199" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -30587,11 +30587,11 @@
         </is>
       </c>
       <c r="I200" s="8" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="J200" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -30637,11 +30637,11 @@
         </is>
       </c>
       <c r="I201" s="8" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
       </c>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -30687,11 +30687,11 @@
         </is>
       </c>
       <c r="I202" s="8" t="n">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -30737,11 +30737,11 @@
         </is>
       </c>
       <c r="I203" s="8" t="n">
-        <v>0.76</v>
+        <v>0.35</v>
       </c>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -30787,7 +30787,7 @@
         </is>
       </c>
       <c r="I204" s="8" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="J204" s="8" t="inlineStr">
         <is>
@@ -30837,11 +30837,11 @@
         </is>
       </c>
       <c r="I205" s="8" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="J205" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -30887,11 +30887,11 @@
         </is>
       </c>
       <c r="I206" s="8" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="J206" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -30937,11 +30937,11 @@
         </is>
       </c>
       <c r="I207" s="8" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="J207" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -30987,11 +30987,11 @@
         </is>
       </c>
       <c r="I208" s="8" t="n">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J208" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -31037,11 +31037,11 @@
         </is>
       </c>
       <c r="I209" s="8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="J209" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -31087,7 +31087,7 @@
         </is>
       </c>
       <c r="I210" s="8" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="J210" s="8" t="inlineStr">
         <is>
@@ -31137,11 +31137,11 @@
         </is>
       </c>
       <c r="I211" s="8" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J211" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -31187,7 +31187,7 @@
         </is>
       </c>
       <c r="I212" s="8" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="J212" s="8" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         </is>
       </c>
       <c r="I213" s="8" t="n">
-        <v>0.51</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J213" s="8" t="inlineStr">
         <is>
@@ -31287,11 +31287,11 @@
         </is>
       </c>
       <c r="I214" s="8" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="J214" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -31337,11 +31337,11 @@
         </is>
       </c>
       <c r="I215" s="8" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="J215" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -31387,11 +31387,11 @@
         </is>
       </c>
       <c r="I216" s="8" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J216" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -31437,7 +31437,7 @@
         </is>
       </c>
       <c r="I217" s="8" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J217" s="8" t="inlineStr">
         <is>
@@ -31487,11 +31487,11 @@
         </is>
       </c>
       <c r="I218" s="8" t="n">
-        <v>0.57</v>
+        <v>0.22</v>
       </c>
       <c r="J218" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -31537,11 +31537,11 @@
         </is>
       </c>
       <c r="I219" s="8" t="n">
-        <v>0.28</v>
+        <v>0.77</v>
       </c>
       <c r="J219" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -31587,11 +31587,11 @@
         </is>
       </c>
       <c r="I220" s="8" t="n">
-        <v>0.67</v>
+        <v>0.21</v>
       </c>
       <c r="J220" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -31637,11 +31637,11 @@
         </is>
       </c>
       <c r="I221" s="8" t="n">
-        <v>0.08</v>
+        <v>0.73</v>
       </c>
       <c r="J221" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="I222" s="8" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="J222" s="8" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
       </c>
       <c r="J223" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -31787,7 +31787,7 @@
         </is>
       </c>
       <c r="I224" s="8" t="n">
-        <v>0.08</v>
+        <v>0.55</v>
       </c>
       <c r="J224" s="8" t="inlineStr">
         <is>
@@ -31837,11 +31837,11 @@
         </is>
       </c>
       <c r="I225" s="8" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -31887,11 +31887,11 @@
         </is>
       </c>
       <c r="I226" s="8" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="J226" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -31937,11 +31937,11 @@
         </is>
       </c>
       <c r="I227" s="8" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="J227" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -31987,11 +31987,11 @@
         </is>
       </c>
       <c r="I228" s="8" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="J228" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -32037,11 +32037,11 @@
         </is>
       </c>
       <c r="I229" s="8" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="J229" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32087,11 +32087,11 @@
         </is>
       </c>
       <c r="I230" s="8" t="n">
-        <v>0.09</v>
+        <v>0.62</v>
       </c>
       <c r="J230" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -32137,11 +32137,11 @@
         </is>
       </c>
       <c r="I231" s="8" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="J231" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32187,7 +32187,7 @@
         </is>
       </c>
       <c r="I232" s="8" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="J232" s="8" t="inlineStr">
         <is>
@@ -32237,11 +32237,11 @@
         </is>
       </c>
       <c r="I233" s="8" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="J233" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -32287,7 +32287,7 @@
         </is>
       </c>
       <c r="I234" s="8" t="n">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="J234" s="8" t="inlineStr">
         <is>
@@ -32337,11 +32337,11 @@
         </is>
       </c>
       <c r="I235" s="8" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="J235" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -32387,11 +32387,11 @@
         </is>
       </c>
       <c r="I236" s="8" t="n">
-        <v>0.57</v>
+        <v>0.2</v>
       </c>
       <c r="J236" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32437,11 +32437,11 @@
         </is>
       </c>
       <c r="I237" s="8" t="n">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="J237" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32487,7 +32487,7 @@
         </is>
       </c>
       <c r="I238" s="8" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="J238" s="8" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="J239" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -32587,7 +32587,7 @@
         </is>
       </c>
       <c r="I240" s="8" t="n">
-        <v>0.39</v>
+        <v>0.72</v>
       </c>
       <c r="J240" s="8" t="inlineStr">
         <is>
@@ -32637,11 +32637,11 @@
         </is>
       </c>
       <c r="I241" s="8" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -32687,11 +32687,11 @@
         </is>
       </c>
       <c r="I242" s="8" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="J242" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32737,7 +32737,7 @@
         </is>
       </c>
       <c r="I243" s="8" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="J243" s="8" t="inlineStr">
         <is>
@@ -32787,11 +32787,11 @@
         </is>
       </c>
       <c r="I244" s="8" t="n">
-        <v>0.74</v>
+        <v>0.52</v>
       </c>
       <c r="J244" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32837,11 +32837,11 @@
         </is>
       </c>
       <c r="I245" s="8" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="J245" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32887,11 +32887,11 @@
         </is>
       </c>
       <c r="I246" s="8" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="J246" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -32937,11 +32937,11 @@
         </is>
       </c>
       <c r="I247" s="8" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="J247" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -32987,11 +32987,11 @@
         </is>
       </c>
       <c r="I248" s="8" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="J248" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33037,11 +33037,11 @@
         </is>
       </c>
       <c r="I249" s="8" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="J249" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33087,11 +33087,11 @@
         </is>
       </c>
       <c r="I250" s="8" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="J250" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33137,11 +33137,11 @@
         </is>
       </c>
       <c r="I251" s="8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J251" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -33187,11 +33187,11 @@
         </is>
       </c>
       <c r="I252" s="8" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="J252" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -33237,7 +33237,7 @@
         </is>
       </c>
       <c r="I253" s="8" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="J253" s="8" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         </is>
       </c>
       <c r="I254" s="8" t="n">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="J254" s="8" t="inlineStr">
         <is>
@@ -33337,11 +33337,11 @@
         </is>
       </c>
       <c r="I255" s="8" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="J255" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="I256" s="8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="J256" s="8" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
       </c>
       <c r="J257" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
         </is>
       </c>
       <c r="I258" s="8" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="J258" s="8" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         </is>
       </c>
       <c r="I259" s="8" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="J259" s="8" t="inlineStr">
         <is>
@@ -33587,11 +33587,11 @@
         </is>
       </c>
       <c r="I260" s="8" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
       </c>
       <c r="J260" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33637,7 +33637,7 @@
         </is>
       </c>
       <c r="I261" s="8" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="J261" s="8" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         </is>
       </c>
       <c r="I262" s="8" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="J262" s="8" t="inlineStr">
         <is>
@@ -33737,11 +33737,11 @@
         </is>
       </c>
       <c r="I263" s="8" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="J263" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33787,11 +33787,11 @@
         </is>
       </c>
       <c r="I264" s="8" t="n">
-        <v>0.77</v>
+        <v>0.37</v>
       </c>
       <c r="J264" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -33837,7 +33837,7 @@
         </is>
       </c>
       <c r="I265" s="8" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J265" s="8" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         </is>
       </c>
       <c r="I266" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="J266" s="8" t="inlineStr">
         <is>
@@ -33937,11 +33937,11 @@
         </is>
       </c>
       <c r="I267" s="8" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="J267" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -33987,7 +33987,7 @@
         </is>
       </c>
       <c r="I268" s="8" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="J268" s="8" t="inlineStr">
         <is>
@@ -34037,11 +34037,11 @@
         </is>
       </c>
       <c r="I269" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="J269" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -34087,11 +34087,11 @@
         </is>
       </c>
       <c r="I270" s="8" t="n">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="J270" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -34137,11 +34137,11 @@
         </is>
       </c>
       <c r="I271" s="8" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="J271" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -34187,11 +34187,11 @@
         </is>
       </c>
       <c r="I272" s="8" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="J272" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -34237,11 +34237,11 @@
         </is>
       </c>
       <c r="I273" s="8" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="J273" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -34287,7 +34287,7 @@
         </is>
       </c>
       <c r="I274" s="8" t="n">
-        <v>0.66</v>
+        <v>0.14</v>
       </c>
       <c r="J274" s="8" t="inlineStr">
         <is>
@@ -34337,11 +34337,11 @@
         </is>
       </c>
       <c r="I275" s="8" t="n">
-        <v>0.23</v>
+        <v>0.74</v>
       </c>
       <c r="J275" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -34387,11 +34387,11 @@
         </is>
       </c>
       <c r="I276" s="8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J276" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -34437,7 +34437,7 @@
         </is>
       </c>
       <c r="I277" s="8" t="n">
-        <v>0.22</v>
+        <v>0.61</v>
       </c>
       <c r="J277" s="8" t="inlineStr">
         <is>
@@ -34487,11 +34487,11 @@
         </is>
       </c>
       <c r="I278" s="8" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="J278" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -34537,11 +34537,11 @@
         </is>
       </c>
       <c r="I279" s="8" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
       <c r="J279" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -34587,11 +34587,11 @@
         </is>
       </c>
       <c r="I280" s="8" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J280" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -34637,7 +34637,7 @@
         </is>
       </c>
       <c r="I281" s="8" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="J281" s="8" t="inlineStr">
         <is>
@@ -34687,11 +34687,11 @@
         </is>
       </c>
       <c r="I282" s="8" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="J282" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -34737,11 +34737,11 @@
         </is>
       </c>
       <c r="I283" s="8" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
       <c r="J283" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -34787,11 +34787,11 @@
         </is>
       </c>
       <c r="I284" s="8" t="n">
-        <v>0.61</v>
+        <v>0.1</v>
       </c>
       <c r="J284" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -34837,7 +34837,7 @@
         </is>
       </c>
       <c r="I285" s="8" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J285" s="8" t="inlineStr">
         <is>
@@ -34887,11 +34887,11 @@
         </is>
       </c>
       <c r="I286" s="8" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="J286" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -34937,11 +34937,11 @@
         </is>
       </c>
       <c r="I287" s="8" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="J287" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -34987,7 +34987,7 @@
         </is>
       </c>
       <c r="I288" s="8" t="n">
-        <v>0.62</v>
+        <v>0.21</v>
       </c>
       <c r="J288" s="8" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         </is>
       </c>
       <c r="I289" s="8" t="n">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="J289" s="8" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         </is>
       </c>
       <c r="I290" s="8" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="J290" s="8" t="inlineStr">
         <is>
@@ -35137,11 +35137,11 @@
         </is>
       </c>
       <c r="I291" s="8" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="J291" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -35187,11 +35187,11 @@
         </is>
       </c>
       <c r="I292" s="8" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="J292" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -35237,11 +35237,11 @@
         </is>
       </c>
       <c r="I293" s="8" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="J293" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -35287,11 +35287,11 @@
         </is>
       </c>
       <c r="I294" s="8" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="J294" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -35337,7 +35337,7 @@
         </is>
       </c>
       <c r="I295" s="8" t="n">
-        <v>0.76</v>
+        <v>0.38</v>
       </c>
       <c r="J295" s="8" t="inlineStr">
         <is>
@@ -35387,11 +35387,11 @@
         </is>
       </c>
       <c r="I296" s="8" t="n">
-        <v>0.09</v>
+        <v>0.57</v>
       </c>
       <c r="J296" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -35437,11 +35437,11 @@
         </is>
       </c>
       <c r="I297" s="8" t="n">
-        <v>0.74</v>
+        <v>0.2</v>
       </c>
       <c r="J297" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -35487,11 +35487,11 @@
         </is>
       </c>
       <c r="I298" s="8" t="n">
-        <v>0.41</v>
+        <v>0.31</v>
       </c>
       <c r="J298" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -35537,11 +35537,11 @@
         </is>
       </c>
       <c r="I299" s="8" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="J299" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -35587,11 +35587,11 @@
         </is>
       </c>
       <c r="I300" s="8" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="J300" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -35637,11 +35637,11 @@
         </is>
       </c>
       <c r="I301" s="8" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="J301" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -35687,11 +35687,11 @@
         </is>
       </c>
       <c r="I302" s="8" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="J302" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -35737,7 +35737,7 @@
         </is>
       </c>
       <c r="I303" s="8" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="J303" s="8" t="inlineStr">
         <is>
@@ -35787,11 +35787,11 @@
         </is>
       </c>
       <c r="I304" s="8" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="J304" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -35837,11 +35837,11 @@
         </is>
       </c>
       <c r="I305" s="8" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="J305" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -35887,7 +35887,7 @@
         </is>
       </c>
       <c r="I306" s="8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J306" s="8" t="inlineStr">
         <is>
@@ -35937,11 +35937,11 @@
         </is>
       </c>
       <c r="I307" s="8" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="J307" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -35987,11 +35987,11 @@
         </is>
       </c>
       <c r="I308" s="8" t="n">
-        <v>0.76</v>
+        <v>0.48</v>
       </c>
       <c r="J308" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -36087,7 +36087,7 @@
         </is>
       </c>
       <c r="I310" s="8" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="J310" s="8" t="inlineStr">
         <is>
@@ -36137,11 +36137,11 @@
         </is>
       </c>
       <c r="I311" s="8" t="n">
-        <v>0.71</v>
+        <v>0.06</v>
       </c>
       <c r="J311" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -36187,11 +36187,11 @@
         </is>
       </c>
       <c r="I312" s="8" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="J312" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -36237,11 +36237,11 @@
         </is>
       </c>
       <c r="I313" s="8" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="J313" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -36287,11 +36287,11 @@
         </is>
       </c>
       <c r="I314" s="8" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="J314" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -36337,11 +36337,11 @@
         </is>
       </c>
       <c r="I315" s="8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="J315" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -36387,11 +36387,11 @@
         </is>
       </c>
       <c r="I316" s="8" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="J316" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -36437,11 +36437,11 @@
         </is>
       </c>
       <c r="I317" s="8" t="n">
-        <v>0.76</v>
+        <v>0.24</v>
       </c>
       <c r="J317" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -36487,11 +36487,11 @@
         </is>
       </c>
       <c r="I318" s="8" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="J318" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -36537,11 +36537,11 @@
         </is>
       </c>
       <c r="I319" s="8" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="J319" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -36587,11 +36587,11 @@
         </is>
       </c>
       <c r="I320" s="8" t="n">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
       <c r="J320" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -36637,11 +36637,11 @@
         </is>
       </c>
       <c r="I321" s="8" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="J321" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -36687,11 +36687,11 @@
         </is>
       </c>
       <c r="I322" s="8" t="n">
-        <v>0.2</v>
+        <v>0.78</v>
       </c>
       <c r="J322" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -36737,11 +36737,11 @@
         </is>
       </c>
       <c r="I323" s="8" t="n">
-        <v>0.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J323" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -36787,7 +36787,7 @@
         </is>
       </c>
       <c r="I324" s="8" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="J324" s="8" t="inlineStr">
         <is>
@@ -36837,11 +36837,11 @@
         </is>
       </c>
       <c r="I325" s="8" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="J325" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -36887,7 +36887,7 @@
         </is>
       </c>
       <c r="I326" s="8" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="J326" s="8" t="inlineStr">
         <is>
@@ -36937,11 +36937,11 @@
         </is>
       </c>
       <c r="I327" s="8" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="J327" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -36987,11 +36987,11 @@
         </is>
       </c>
       <c r="I328" s="8" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="J328" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
         </is>
       </c>
       <c r="I329" s="8" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="J329" s="8" t="inlineStr">
         <is>
@@ -37087,11 +37087,11 @@
         </is>
       </c>
       <c r="I330" s="8" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="J330" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -37137,11 +37137,11 @@
         </is>
       </c>
       <c r="I331" s="8" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="J331" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -37187,7 +37187,7 @@
         </is>
       </c>
       <c r="I332" s="8" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="J332" s="8" t="inlineStr">
         <is>
@@ -37237,11 +37237,11 @@
         </is>
       </c>
       <c r="I333" s="8" t="n">
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
       <c r="J333" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -37287,7 +37287,7 @@
         </is>
       </c>
       <c r="I334" s="8" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="J334" s="8" t="inlineStr">
         <is>
@@ -37337,11 +37337,11 @@
         </is>
       </c>
       <c r="I335" s="8" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="J335" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -37387,11 +37387,11 @@
         </is>
       </c>
       <c r="I336" s="8" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="J336" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -37437,11 +37437,11 @@
         </is>
       </c>
       <c r="I337" s="8" t="n">
-        <v>0.58</v>
+        <v>0.21</v>
       </c>
       <c r="J337" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -37487,7 +37487,7 @@
         </is>
       </c>
       <c r="I338" s="8" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="J338" s="8" t="inlineStr">
         <is>
@@ -37537,11 +37537,11 @@
         </is>
       </c>
       <c r="I339" s="8" t="n">
-        <v>0.06</v>
+        <v>0.67</v>
       </c>
       <c r="J339" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -37587,11 +37587,11 @@
         </is>
       </c>
       <c r="I340" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="J340" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -37637,11 +37637,11 @@
         </is>
       </c>
       <c r="I341" s="8" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="J341" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -37687,11 +37687,11 @@
         </is>
       </c>
       <c r="I342" s="8" t="n">
-        <v>0.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J342" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -37737,11 +37737,11 @@
         </is>
       </c>
       <c r="I343" s="8" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="J343" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -37787,11 +37787,11 @@
         </is>
       </c>
       <c r="I344" s="8" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="J344" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -37837,11 +37837,11 @@
         </is>
       </c>
       <c r="I345" s="8" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="J345" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -37887,7 +37887,7 @@
         </is>
       </c>
       <c r="I346" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="J346" s="8" t="inlineStr">
         <is>
@@ -37937,11 +37937,11 @@
         </is>
       </c>
       <c r="I347" s="8" t="n">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="J347" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -37987,7 +37987,7 @@
         </is>
       </c>
       <c r="I348" s="8" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="J348" s="8" t="inlineStr">
         <is>
@@ -38037,11 +38037,11 @@
         </is>
       </c>
       <c r="I349" s="8" t="n">
-        <v>0.24</v>
+        <v>0.66</v>
       </c>
       <c r="J349" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -38087,11 +38087,11 @@
         </is>
       </c>
       <c r="I350" s="8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J350" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -38137,11 +38137,11 @@
         </is>
       </c>
       <c r="I351" s="8" t="n">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="J351" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -38187,7 +38187,7 @@
         </is>
       </c>
       <c r="I352" s="8" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="J352" s="8" t="inlineStr">
         <is>
@@ -38237,11 +38237,11 @@
         </is>
       </c>
       <c r="I353" s="8" t="n">
-        <v>0.63</v>
+        <v>0.44</v>
       </c>
       <c r="J353" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -38287,11 +38287,11 @@
         </is>
       </c>
       <c r="I354" s="8" t="n">
-        <v>0.05</v>
+        <v>0.49</v>
       </c>
       <c r="J354" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -38387,11 +38387,11 @@
         </is>
       </c>
       <c r="I356" s="8" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="J356" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="I357" s="8" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="J357" s="8" t="inlineStr">
         <is>
@@ -38487,11 +38487,11 @@
         </is>
       </c>
       <c r="I358" s="8" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="J358" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -38537,11 +38537,11 @@
         </is>
       </c>
       <c r="I359" s="8" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="J359" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -38587,11 +38587,11 @@
         </is>
       </c>
       <c r="I360" s="8" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="J360" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -38637,11 +38637,11 @@
         </is>
       </c>
       <c r="I361" s="8" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="J361" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -38687,11 +38687,11 @@
         </is>
       </c>
       <c r="I362" s="8" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="J362" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -38737,11 +38737,11 @@
         </is>
       </c>
       <c r="I363" s="8" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="J363" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -38787,11 +38787,11 @@
         </is>
       </c>
       <c r="I364" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="J364" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -38837,11 +38837,11 @@
         </is>
       </c>
       <c r="I365" s="8" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="J365" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -38887,11 +38887,11 @@
         </is>
       </c>
       <c r="I366" s="8" t="n">
-        <v>0.75</v>
+        <v>0.08</v>
       </c>
       <c r="J366" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -38937,7 +38937,7 @@
         </is>
       </c>
       <c r="I367" s="8" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="J367" s="8" t="inlineStr">
         <is>
@@ -38987,11 +38987,11 @@
         </is>
       </c>
       <c r="I368" s="8" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="J368" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -39037,11 +39037,11 @@
         </is>
       </c>
       <c r="I369" s="8" t="n">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="J369" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -39087,7 +39087,7 @@
         </is>
       </c>
       <c r="I370" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="J370" s="8" t="inlineStr">
         <is>
@@ -39137,11 +39137,11 @@
         </is>
       </c>
       <c r="I371" s="8" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="J371" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -39187,11 +39187,11 @@
         </is>
       </c>
       <c r="I372" s="8" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="J372" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -39237,7 +39237,7 @@
         </is>
       </c>
       <c r="I373" s="8" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="J373" s="8" t="inlineStr">
         <is>
@@ -39287,11 +39287,11 @@
         </is>
       </c>
       <c r="I374" s="8" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="J374" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -39337,11 +39337,11 @@
         </is>
       </c>
       <c r="I375" s="8" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J375" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -39387,11 +39387,11 @@
         </is>
       </c>
       <c r="I376" s="8" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="J376" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -39437,11 +39437,11 @@
         </is>
       </c>
       <c r="I377" s="8" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="J377" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -39487,11 +39487,11 @@
         </is>
       </c>
       <c r="I378" s="8" t="n">
-        <v>0.18</v>
+        <v>0.68</v>
       </c>
       <c r="J378" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -39537,11 +39537,11 @@
         </is>
       </c>
       <c r="I379" s="8" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="J379" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -39587,7 +39587,7 @@
         </is>
       </c>
       <c r="I380" s="8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J380" s="8" t="inlineStr">
         <is>
@@ -39637,11 +39637,11 @@
         </is>
       </c>
       <c r="I381" s="8" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J381" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -39687,11 +39687,11 @@
         </is>
       </c>
       <c r="I382" s="8" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="J382" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -39737,11 +39737,11 @@
         </is>
       </c>
       <c r="I383" s="8" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="J383" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -39787,7 +39787,7 @@
         </is>
       </c>
       <c r="I384" s="8" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="J384" s="8" t="inlineStr">
         <is>
@@ -39837,11 +39837,11 @@
         </is>
       </c>
       <c r="I385" s="8" t="n">
-        <v>0.11</v>
+        <v>0.59</v>
       </c>
       <c r="J385" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -39887,11 +39887,11 @@
         </is>
       </c>
       <c r="I386" s="8" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J386" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -39987,11 +39987,11 @@
         </is>
       </c>
       <c r="I388" s="8" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="J388" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -40037,11 +40037,11 @@
         </is>
       </c>
       <c r="I389" s="8" t="n">
-        <v>0.39</v>
+        <v>0.74</v>
       </c>
       <c r="J389" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -40087,11 +40087,11 @@
         </is>
       </c>
       <c r="I390" s="8" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="J390" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -40137,11 +40137,11 @@
         </is>
       </c>
       <c r="I391" s="8" t="n">
-        <v>0.25</v>
+        <v>0.77</v>
       </c>
       <c r="J391" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -40187,7 +40187,7 @@
         </is>
       </c>
       <c r="I392" s="8" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="J392" s="8" t="inlineStr">
         <is>
@@ -40237,11 +40237,11 @@
         </is>
       </c>
       <c r="I393" s="8" t="n">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
       <c r="J393" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -40287,7 +40287,7 @@
         </is>
       </c>
       <c r="I394" s="8" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="J394" s="8" t="inlineStr">
         <is>
@@ -40337,11 +40337,11 @@
         </is>
       </c>
       <c r="I395" s="8" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="J395" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -40387,11 +40387,11 @@
         </is>
       </c>
       <c r="I396" s="8" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="J396" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -40437,11 +40437,11 @@
         </is>
       </c>
       <c r="I397" s="8" t="n">
-        <v>0.76</v>
+        <v>0.61</v>
       </c>
       <c r="J397" s="8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -40487,11 +40487,11 @@
         </is>
       </c>
       <c r="I398" s="8" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="J398" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -40537,11 +40537,11 @@
         </is>
       </c>
       <c r="I399" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="J399" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -40587,7 +40587,7 @@
         </is>
       </c>
       <c r="I400" s="8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="J400" s="8" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         </is>
       </c>
       <c r="I401" s="8" t="n">
-        <v>0.74</v>
+        <v>0.32</v>
       </c>
       <c r="J401" s="8" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>168.61 seconds</t>
+          <t>166.61 seconds</t>
         </is>
       </c>
     </row>
@@ -40857,7 +40857,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 13:48:44</t>
+          <t>2026-07-27 14:05:04</t>
         </is>
       </c>
     </row>
